--- a/ig/DM-OCTOBRE-2025/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2025/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="181">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20251028120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-10-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>83901-9</t>
+  </si>
+  <si>
+    <t>83963-9</t>
   </si>
   <si>
     <t>83981-1</t>
@@ -816,7 +819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1915,7 +1918,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1941,7 +1944,7 @@
         <v>33</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1954,7 +1957,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -1967,7 +1970,7 @@
         <v>33</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -1980,7 +1983,7 @@
         <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -2006,7 +2009,7 @@
         <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2019,7 +2022,7 @@
         <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2045,7 +2048,7 @@
         <v>33</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E94" s="2"/>
     </row>
@@ -2071,7 +2074,7 @@
         <v>33</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E96" s="2"/>
     </row>
@@ -2087,6 +2090,19 @@
         <v>34</v>
       </c>
       <c r="E97" s="2"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E98" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2117,7 +2133,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2134,7 +2150,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2147,7 +2163,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2160,7 +2176,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2173,7 +2189,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2186,7 +2202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2199,7 +2215,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2212,7 +2228,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2225,7 +2241,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2238,7 +2254,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2251,7 +2267,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2264,7 +2280,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2277,7 +2293,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2290,7 +2306,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2303,7 +2319,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2316,7 +2332,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2329,7 +2345,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2342,7 +2358,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2355,7 +2371,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2368,7 +2384,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2381,7 +2397,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2394,7 +2410,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2407,7 +2423,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2420,7 +2436,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -2433,20 +2449,20 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2459,7 +2475,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2472,7 +2488,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -2485,7 +2501,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2498,7 +2514,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2511,7 +2527,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2524,7 +2540,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2537,7 +2553,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2550,7 +2566,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2563,20 +2579,20 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2616,7 +2632,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2625,7 +2641,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -2633,14 +2649,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/DM-OCTOBRE-2025/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2025/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -308,6 +308,12 @@
     <t>61357-0</t>
   </si>
   <si>
+    <t>61358-8</t>
+  </si>
+  <si>
+    <t>61359-6</t>
+  </si>
+  <si>
     <t>67851-6</t>
   </si>
   <si>
@@ -434,6 +440,9 @@
     <t>100967-9</t>
   </si>
   <si>
+    <t>101881-1</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -449,6 +458,9 @@
     <t>ATTEST-DROITS-AM</t>
   </si>
   <si>
+    <t>ATTEST-VITALE</t>
+  </si>
+  <si>
     <t>AUTORIS-SOINS</t>
   </si>
   <si>
@@ -458,6 +470,9 @@
     <t>CERT_DECL</t>
   </si>
   <si>
+    <t>CONTACTS-URGENCE</t>
+  </si>
+  <si>
     <t>DISP_AUT</t>
   </si>
   <si>
@@ -498,6 +513,9 @@
   </si>
   <si>
     <t>DOCPAT09</t>
+  </si>
+  <si>
+    <t>DOCPAT10</t>
   </si>
   <si>
     <t>IMG-KOS</t>
@@ -819,7 +837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1593,7 +1611,7 @@
         <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1606,7 +1624,7 @@
         <v>33</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1671,33 +1689,33 @@
         <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="E67" s="2"/>
     </row>
@@ -1710,7 +1728,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -1762,7 +1780,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -1775,7 +1793,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -1788,7 +1806,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1801,7 +1819,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1814,7 +1832,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E76" s="2"/>
     </row>
@@ -1827,33 +1845,33 @@
         <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="E79" s="2"/>
     </row>
@@ -1866,7 +1884,7 @@
         <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1879,7 +1897,7 @@
         <v>33</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -1892,7 +1910,7 @@
         <v>33</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1918,7 +1936,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1931,7 +1949,7 @@
         <v>33</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1944,7 +1962,7 @@
         <v>33</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1957,7 +1975,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -1970,7 +1988,7 @@
         <v>33</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -1983,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -1996,7 +2014,7 @@
         <v>33</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2009,7 +2027,7 @@
         <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2022,7 +2040,7 @@
         <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2035,7 +2053,7 @@
         <v>33</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2048,7 +2066,7 @@
         <v>33</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E94" s="2"/>
     </row>
@@ -2061,7 +2079,7 @@
         <v>33</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E95" s="2"/>
     </row>
@@ -2074,7 +2092,7 @@
         <v>33</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E96" s="2"/>
     </row>
@@ -2087,7 +2105,7 @@
         <v>33</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E97" s="2"/>
     </row>
@@ -2100,9 +2118,48 @@
         <v>33</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E98" s="2"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B99" s="2"/>
+      <c r="C99" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E101" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2111,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2133,7 +2190,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2150,7 +2207,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2163,7 +2220,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2176,7 +2233,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2189,7 +2246,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2202,7 +2259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2215,98 +2272,98 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2319,46 +2376,46 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2371,150 +2428,150 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2527,20 +2584,20 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2553,7 +2610,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2566,7 +2623,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2579,29 +2636,68 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D40" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E40" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2632,7 +2728,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2641,7 +2737,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -2649,14 +2745,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2"/>
     </row>
